--- a/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.167.xlsx
+++ b/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.167.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="oocihm.22250.167" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="oocihm.22250.167" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -581,12 +581,12 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.167.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.167.txt</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0167.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0167.txt</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr"/>
@@ -883,7 +883,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.167.xlsx
+++ b/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.167.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="oocihm.22250.167" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="oocihm.22250.167" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -416,14 +416,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y57"/>
+  <dimension ref="A1:Y62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
     <col width="35" customWidth="1" min="7" max="7"/>
     <col width="60" customWidth="1" min="8" max="8"/>
@@ -431,7 +431,7 @@
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
     <col width="60" customWidth="1" min="14" max="14"/>
     <col width="60" customWidth="1" min="15" max="15"/>
     <col width="31" customWidth="1" min="16" max="16"/>
@@ -599,22 +599,26 @@
       <c r="G2" s="1" t="inlineStr"/>
       <c r="H2" s="1" t="inlineStr">
         <is>
-          <t>L4: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): EQuITy (odd internal casing) :: BILL IN EQuITy â€” Continued.</t>
+          <t>L4: suspicious token(s): EQuITy (odd internal casing) :: BILL IN EQuITy — Continued.</t>
         </is>
       </c>
       <c r="I2" s="1" t="inlineStr"/>
       <c r="J2" s="1" t="inlineStr">
         <is>
-          <t>L4: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): EQuITy (odd internal casing) :: BILL IN EQuITy â€” Continued.</t>
+          <t>L41: stray/suspicious non-ASCII glyph(s): U+25CF BLACK CIRCLE | isolated marker/symbol line :: ●</t>
         </is>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L7: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: BILL IN Equityâ€”Continued.</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]160</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]160</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L1: isolated marker/symbol line :: 160</t>
@@ -622,7 +626,7 @@
       </c>
       <c r="O2" s="1" t="inlineStr">
         <is>
-          <t>L19: isolated marker/symbol line :: E</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]160</t>
         </is>
       </c>
       <c r="P2" s="1" t="inlineStr"/>
@@ -653,7 +657,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>93</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -668,12 +672,12 @@
       <c r="I3" s="1" t="inlineStr"/>
       <c r="J3" s="1" t="inlineStr">
         <is>
-          <t>L30: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Orders. (See Speeding the Cause.) 70-71 â€” 72</t>
+          <t>L44: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
         </is>
       </c>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>L32: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 46â€”47</t>
+          <t>L64: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L3" s="1" t="inlineStr"/>
@@ -685,7 +689,7 @@
       </c>
       <c r="O3" s="1" t="inlineStr">
         <is>
-          <t>L23: isolated marker/symbol line :: S</t>
+          <t>L19: isolated marker/symbol line :: E</t>
         </is>
       </c>
       <c r="P3" s="1" t="inlineStr"/>
@@ -725,18 +729,18 @@
       <c r="G4" s="1" t="inlineStr"/>
       <c r="H4" s="1" t="inlineStr">
         <is>
-          <t>L68: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): EQuITy (odd internal casing) :: BILL IN EQuITy â€” Continued.</t>
+          <t>L68: suspicious token(s): EQuITy (odd internal casing) :: BILL IN EQuITy — Continued.</t>
         </is>
       </c>
       <c r="I4" s="1" t="inlineStr"/>
       <c r="J4" s="1" t="inlineStr">
         <is>
-          <t>L36: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 111 â€” 112</t>
+          <t>L60: stray/suspicious non-ASCII glyph(s): U+5206 CJK UNIFIED IDEOGRAPH-5206 | isolated marker/symbol line :: 分</t>
         </is>
       </c>
       <c r="K4" s="1" t="inlineStr">
         <is>
-          <t>L35: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Whether dismissal of Bill a Bar to another suit . 70â€”71</t>
+          <t>L107: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L4" s="1" t="inlineStr"/>
@@ -748,7 +752,7 @@
       </c>
       <c r="O4" s="1" t="inlineStr">
         <is>
-          <t>L24: isolated marker/symbol line :: 0</t>
+          <t>L23: isolated marker/symbol line :: S</t>
         </is>
       </c>
       <c r="P4" s="1" t="inlineStr"/>
@@ -770,12 +774,12 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>66</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>45</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr"/>
@@ -790,12 +794,12 @@
       <c r="I5" s="1" t="inlineStr"/>
       <c r="J5" s="1" t="inlineStr">
         <is>
-          <t>L41: stray/suspicious non-ASCII glyph(s): U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: â—�</t>
+          <t>L104: stray/suspicious non-ASCII glyph(s): U+221A SQUARE ROOT | isolated marker/symbol line :: √</t>
         </is>
       </c>
       <c r="K5" s="1" t="inlineStr">
         <is>
-          <t>L64: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L155: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L5" s="1" t="inlineStr"/>
@@ -807,7 +811,7 @@
       </c>
       <c r="O5" s="1" t="inlineStr">
         <is>
-          <t>L25: isolated marker/symbol line :: T</t>
+          <t>L24: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="P5" s="1" t="inlineStr"/>
@@ -849,14 +853,10 @@
       <c r="I6" s="1" t="inlineStr"/>
       <c r="J6" s="1" t="inlineStr">
         <is>
-          <t>L44: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
-        </is>
-      </c>
-      <c r="K6" s="1" t="inlineStr">
-        <is>
-          <t>L77: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: . 115â€”116</t>
-        </is>
-      </c>
+          <t>L122: stray/suspicious non-ASCII glyph(s): U+25CF BLACK CIRCLE | isolated marker/symbol line :: ●</t>
+        </is>
+      </c>
+      <c r="K6" s="1" t="inlineStr"/>
       <c r="L6" s="1" t="inlineStr"/>
       <c r="M6" s="1" t="inlineStr"/>
       <c r="N6" s="1" t="inlineStr">
@@ -866,7 +866,7 @@
       </c>
       <c r="O6" s="1" t="inlineStr">
         <is>
-          <t>L27: isolated marker/symbol line :: 23</t>
+          <t>L25: isolated marker/symbol line :: T</t>
         </is>
       </c>
       <c r="P6" s="1" t="inlineStr"/>
@@ -904,14 +904,10 @@
       <c r="I7" s="1" t="inlineStr"/>
       <c r="J7" s="1" t="inlineStr">
         <is>
-          <t>L68: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): EQuITy (odd internal casing) :: BILL IN EQuITy â€” Continued.</t>
-        </is>
-      </c>
-      <c r="K7" s="1" t="inlineStr">
-        <is>
-          <t>L91: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Orders. (See" Speeding the Cause.") 70â€”71â€”72</t>
-        </is>
-      </c>
+          <t>L126: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
+        </is>
+      </c>
+      <c r="K7" s="1" t="inlineStr"/>
       <c r="L7" s="1" t="inlineStr"/>
       <c r="M7" s="1" t="inlineStr"/>
       <c r="N7" s="1" t="inlineStr">
@@ -921,7 +917,7 @@
       </c>
       <c r="O7" s="1" t="inlineStr">
         <is>
-          <t>L29: isolated marker/symbol line :: 20</t>
+          <t>L27: isolated marker/symbol line :: 23</t>
         </is>
       </c>
       <c r="P7" s="1" t="inlineStr"/>
@@ -959,14 +955,10 @@
       <c r="I8" s="1" t="inlineStr"/>
       <c r="J8" s="1" t="inlineStr">
         <is>
-          <t>L105: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Orders. (See Speeding the Cause.) 70-71 â€” 72</t>
-        </is>
-      </c>
-      <c r="K8" s="1" t="inlineStr">
-        <is>
-          <t>L99: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 69â€”70</t>
-        </is>
-      </c>
+          <t>L130: stray/suspicious non-ASCII glyph(s): U+4E00 CJK UNIFIED IDEOGRAPH-4E00 | isolated marker/symbol line :: 一</t>
+        </is>
+      </c>
+      <c r="K8" s="1" t="inlineStr"/>
       <c r="L8" s="1" t="inlineStr"/>
       <c r="M8" s="1" t="inlineStr"/>
       <c r="N8" s="1" t="inlineStr">
@@ -976,7 +968,7 @@
       </c>
       <c r="O8" s="1" t="inlineStr">
         <is>
-          <t>L30: isolated marker/symbol line :: 24</t>
+          <t>L29: isolated marker/symbol line :: 20</t>
         </is>
       </c>
       <c r="P8" s="1" t="inlineStr"/>
@@ -1014,14 +1006,10 @@
       <c r="I9" s="1" t="inlineStr"/>
       <c r="J9" s="1" t="inlineStr">
         <is>
-          <t>L114: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 111 â€” 112</t>
-        </is>
-      </c>
-      <c r="K9" s="1" t="inlineStr">
-        <is>
-          <t>L105: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: . 111â€”112</t>
-        </is>
-      </c>
+          <t>L146: stray/suspicious non-ASCII glyph(s): U+5206 CJK UNIFIED IDEOGRAPH-5206 | isolated marker/symbol line :: 分</t>
+        </is>
+      </c>
+      <c r="K9" s="1" t="inlineStr"/>
       <c r="L9" s="1" t="inlineStr"/>
       <c r="M9" s="1" t="inlineStr"/>
       <c r="N9" s="1" t="inlineStr">
@@ -1031,7 +1019,7 @@
       </c>
       <c r="O9" s="1" t="inlineStr">
         <is>
-          <t>L45: isolated marker/symbol line :: 0</t>
+          <t>L30: isolated marker/symbol line :: 24</t>
         </is>
       </c>
       <c r="P9" s="1" t="inlineStr"/>
@@ -1053,12 +1041,12 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr"/>
@@ -1067,16 +1055,8 @@
       <c r="G10" s="1" t="inlineStr"/>
       <c r="H10" s="1" t="inlineStr"/>
       <c r="I10" s="1" t="inlineStr"/>
-      <c r="J10" s="1" t="inlineStr">
-        <is>
-          <t>L122: stray/suspicious non-ASCII glyph(s): U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: â—�</t>
-        </is>
-      </c>
-      <c r="K10" s="1" t="inlineStr">
-        <is>
-          <t>L107: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
-        </is>
-      </c>
+      <c r="J10" s="1" t="inlineStr"/>
+      <c r="K10" s="1" t="inlineStr"/>
       <c r="L10" s="1" t="inlineStr"/>
       <c r="M10" s="1" t="inlineStr"/>
       <c r="N10" s="1" t="inlineStr">
@@ -1086,7 +1066,7 @@
       </c>
       <c r="O10" s="1" t="inlineStr">
         <is>
-          <t>L49: isolated marker/symbol line :: S</t>
+          <t>L32: symbol-only separator/garbage line :: 46—47</t>
         </is>
       </c>
       <c r="P10" s="1" t="inlineStr"/>
@@ -1113,7 +1093,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1122,16 +1102,8 @@
       <c r="G11" s="1" t="inlineStr"/>
       <c r="H11" s="1" t="inlineStr"/>
       <c r="I11" s="1" t="inlineStr"/>
-      <c r="J11" s="1" t="inlineStr">
-        <is>
-          <t>L126: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
-        </is>
-      </c>
-      <c r="K11" s="1" t="inlineStr">
-        <is>
-          <t>L117: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+02DC SMALL TILDE :: Cases in which/the Court gives Relief .â€˜</t>
-        </is>
-      </c>
+      <c r="J11" s="1" t="inlineStr"/>
+      <c r="K11" s="1" t="inlineStr"/>
       <c r="L11" s="1" t="inlineStr"/>
       <c r="M11" s="1" t="inlineStr"/>
       <c r="N11" s="1" t="inlineStr">
@@ -1141,7 +1113,7 @@
       </c>
       <c r="O11" s="1" t="inlineStr">
         <is>
-          <t>L51: isolated marker/symbol line :: I</t>
+          <t>L45: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="P11" s="1" t="inlineStr"/>
@@ -1163,12 +1135,12 @@
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>61</t>
         </is>
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>43</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr"/>
@@ -1177,26 +1149,18 @@
       <c r="G12" s="1" t="inlineStr"/>
       <c r="H12" s="1" t="inlineStr"/>
       <c r="I12" s="1" t="inlineStr"/>
-      <c r="J12" s="1" t="inlineStr">
-        <is>
-          <t>L130: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA, U+20AC EURO SIGN | isolated marker/symbol line :: ä¸€</t>
-        </is>
-      </c>
-      <c r="K12" s="1" t="inlineStr">
-        <is>
-          <t>L145: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: . 7â€”10</t>
-        </is>
-      </c>
+      <c r="J12" s="1" t="inlineStr"/>
+      <c r="K12" s="1" t="inlineStr"/>
       <c r="L12" s="1" t="inlineStr"/>
       <c r="M12" s="1" t="inlineStr"/>
       <c r="N12" s="1" t="inlineStr">
         <is>
-          <t>L38: isolated marker/symbol line :: 116</t>
+          <t>L36: symbol-only separator/garbage line :: 111 — 112</t>
         </is>
       </c>
       <c r="O12" s="1" t="inlineStr">
         <is>
-          <t>L52: isolated marker/symbol line :: C</t>
+          <t>L49: isolated marker/symbol line :: S</t>
         </is>
       </c>
       <c r="P12" s="1" t="inlineStr"/>
@@ -1233,21 +1197,17 @@
       <c r="H13" s="1" t="inlineStr"/>
       <c r="I13" s="1" t="inlineStr"/>
       <c r="J13" s="1" t="inlineStr"/>
-      <c r="K13" s="1" t="inlineStr">
-        <is>
-          <t>L155: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
-        </is>
-      </c>
+      <c r="K13" s="1" t="inlineStr"/>
       <c r="L13" s="1" t="inlineStr"/>
       <c r="M13" s="1" t="inlineStr"/>
       <c r="N13" s="1" t="inlineStr">
         <is>
-          <t>L41: stray/suspicious non-ASCII glyph(s): U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: â—�</t>
+          <t>L38: isolated marker/symbol line :: 116</t>
         </is>
       </c>
       <c r="O13" s="1" t="inlineStr">
         <is>
-          <t>L53: isolated marker/symbol line :: C</t>
+          <t>L51: isolated marker/symbol line :: I</t>
         </is>
       </c>
       <c r="P13" s="1" t="inlineStr"/>
@@ -1289,12 +1249,12 @@
       <c r="M14" s="1" t="inlineStr"/>
       <c r="N14" s="1" t="inlineStr">
         <is>
-          <t>L42: isolated marker/symbol line :: 2</t>
+          <t>L41: stray/suspicious non-ASCII glyph(s): U+25CF BLACK CIRCLE | isolated marker/symbol line :: ●</t>
         </is>
       </c>
       <c r="O14" s="1" t="inlineStr">
         <is>
-          <t>L54: isolated marker/symbol line :: C</t>
+          <t>L52: isolated marker/symbol line :: C</t>
         </is>
       </c>
       <c r="P14" s="1" t="inlineStr"/>
@@ -1336,12 +1296,12 @@
       <c r="M15" s="1" t="inlineStr"/>
       <c r="N15" s="1" t="inlineStr">
         <is>
-          <t>L44: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
+          <t>L42: isolated marker/symbol line :: 2</t>
         </is>
       </c>
       <c r="O15" s="1" t="inlineStr">
         <is>
-          <t>L55: isolated marker/symbol line :: A</t>
+          <t>L53: isolated marker/symbol line :: C</t>
         </is>
       </c>
       <c r="P15" s="1" t="inlineStr"/>
@@ -1383,12 +1343,12 @@
       <c r="M16" s="1" t="inlineStr"/>
       <c r="N16" s="1" t="inlineStr">
         <is>
-          <t>L49: symbol-only separator/garbage line :: . 7-10</t>
+          <t>L44: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
         </is>
       </c>
       <c r="O16" s="1" t="inlineStr">
         <is>
-          <t>L57: isolated marker/symbol line :: I</t>
+          <t>L54: isolated marker/symbol line :: C</t>
         </is>
       </c>
       <c r="P16" s="1" t="inlineStr"/>
@@ -1430,12 +1390,12 @@
       <c r="M17" s="1" t="inlineStr"/>
       <c r="N17" s="1" t="inlineStr">
         <is>
-          <t>L51: isolated marker/symbol line :: 7</t>
+          <t>L49: symbol-only separator/garbage line :: . 7-10</t>
         </is>
       </c>
       <c r="O17" s="1" t="inlineStr">
         <is>
-          <t>L58: isolated marker/symbol line :: s</t>
+          <t>L55: isolated marker/symbol line :: A</t>
         </is>
       </c>
       <c r="P17" s="1" t="inlineStr"/>
@@ -1465,12 +1425,12 @@
       <c r="M18" s="1" t="inlineStr"/>
       <c r="N18" s="1" t="inlineStr">
         <is>
-          <t>L53: isolated marker/symbol line :: B</t>
+          <t>L51: isolated marker/symbol line :: 7</t>
         </is>
       </c>
       <c r="O18" s="1" t="inlineStr">
         <is>
-          <t>L61: isolated marker/symbol line :: z</t>
+          <t>L57: isolated marker/symbol line :: I</t>
         </is>
       </c>
       <c r="P18" s="1" t="inlineStr"/>
@@ -1500,12 +1460,12 @@
       <c r="M19" s="1" t="inlineStr"/>
       <c r="N19" s="1" t="inlineStr">
         <is>
-          <t>L54: isolated marker/symbol line :: 10</t>
+          <t>L53: isolated marker/symbol line :: B</t>
         </is>
       </c>
       <c r="O19" s="1" t="inlineStr">
         <is>
-          <t>L64: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L58: isolated marker/symbol line :: s</t>
         </is>
       </c>
       <c r="P19" s="1" t="inlineStr"/>
@@ -1535,12 +1495,12 @@
       <c r="M20" s="1" t="inlineStr"/>
       <c r="N20" s="1" t="inlineStr">
         <is>
-          <t>L58: isolated marker/symbol line :: 12</t>
+          <t>L54: isolated marker/symbol line :: 10</t>
         </is>
       </c>
       <c r="O20" s="1" t="inlineStr">
         <is>
-          <t>L65: isolated marker/symbol line :: s</t>
+          <t>L61: isolated marker/symbol line :: z</t>
         </is>
       </c>
       <c r="P20" s="1" t="inlineStr"/>
@@ -1570,12 +1530,12 @@
       <c r="M21" s="1" t="inlineStr"/>
       <c r="N21" s="1" t="inlineStr">
         <is>
-          <t>L62: isolated marker/symbol line :: 10</t>
+          <t>L58: isolated marker/symbol line :: 12</t>
         </is>
       </c>
       <c r="O21" s="1" t="inlineStr">
         <is>
-          <t>L66: isolated marker/symbol line :: I</t>
+          <t>L64: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P21" s="1" t="inlineStr"/>
@@ -1605,12 +1565,12 @@
       <c r="M22" s="1" t="inlineStr"/>
       <c r="N22" s="1" t="inlineStr">
         <is>
-          <t>L64: isolated marker/symbol line :: 7</t>
+          <t>L60: stray/suspicious non-ASCII glyph(s): U+5206 CJK UNIFIED IDEOGRAPH-5206 | isolated marker/symbol line :: 分</t>
         </is>
       </c>
       <c r="O22" s="1" t="inlineStr">
         <is>
-          <t>L67: isolated marker/symbol line :: 1</t>
+          <t>L65: isolated marker/symbol line :: s</t>
         </is>
       </c>
       <c r="P22" s="1" t="inlineStr"/>
@@ -1640,12 +1600,12 @@
       <c r="M23" s="1" t="inlineStr"/>
       <c r="N23" s="1" t="inlineStr">
         <is>
-          <t>L65: isolated marker/symbol line :: 160</t>
+          <t>L62: isolated marker/symbol line :: 10</t>
         </is>
       </c>
       <c r="O23" s="1" t="inlineStr">
         <is>
-          <t>L69: isolated marker/symbol line :: I</t>
+          <t>L66: isolated marker/symbol line :: I</t>
         </is>
       </c>
       <c r="P23" s="1" t="inlineStr"/>
@@ -1675,12 +1635,12 @@
       <c r="M24" s="1" t="inlineStr"/>
       <c r="N24" s="1" t="inlineStr">
         <is>
-          <t>L71: isolated marker/symbol line :: 23</t>
+          <t>L64: isolated marker/symbol line :: 7</t>
         </is>
       </c>
       <c r="O24" s="1" t="inlineStr">
         <is>
-          <t>L72: isolated marker/symbol line :: I</t>
+          <t>L67: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="P24" s="1" t="inlineStr"/>
@@ -1710,12 +1670,12 @@
       <c r="M25" s="1" t="inlineStr"/>
       <c r="N25" s="1" t="inlineStr">
         <is>
-          <t>L72: isolated marker/symbol line :: E</t>
+          <t>L65: isolated marker/symbol line :: 160</t>
         </is>
       </c>
       <c r="O25" s="1" t="inlineStr">
         <is>
-          <t>L75: isolated marker/symbol line :: ]</t>
+          <t>L69: isolated marker/symbol line :: I</t>
         </is>
       </c>
       <c r="P25" s="1" t="inlineStr"/>
@@ -1745,12 +1705,12 @@
       <c r="M26" s="1" t="inlineStr"/>
       <c r="N26" s="1" t="inlineStr">
         <is>
-          <t>L76: isolated marker/symbol line :: 20</t>
+          <t>L71: isolated marker/symbol line :: 23</t>
         </is>
       </c>
       <c r="O26" s="1" t="inlineStr">
         <is>
-          <t>L101: symbol-only separator/garbage line :: . 108</t>
+          <t>L72: isolated marker/symbol line :: I</t>
         </is>
       </c>
       <c r="P26" s="1" t="inlineStr"/>
@@ -1780,12 +1740,12 @@
       <c r="M27" s="1" t="inlineStr"/>
       <c r="N27" s="1" t="inlineStr">
         <is>
-          <t>L77: isolated marker/symbol line :: S</t>
+          <t>L72: isolated marker/symbol line :: E</t>
         </is>
       </c>
       <c r="O27" s="1" t="inlineStr">
         <is>
-          <t>L103: isolated marker/symbol line :: 109</t>
+          <t>L75: isolated marker/symbol line :: ]</t>
         </is>
       </c>
       <c r="P27" s="1" t="inlineStr"/>
@@ -1815,12 +1775,12 @@
       <c r="M28" s="1" t="inlineStr"/>
       <c r="N28" s="1" t="inlineStr">
         <is>
-          <t>L79: isolated marker/symbol line :: 24</t>
+          <t>L76: isolated marker/symbol line :: 20</t>
         </is>
       </c>
       <c r="O28" s="1" t="inlineStr">
         <is>
-          <t>L107: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L77: symbol-only separator/garbage line :: . 115—116</t>
         </is>
       </c>
       <c r="P28" s="1" t="inlineStr"/>
@@ -1850,12 +1810,12 @@
       <c r="M29" s="1" t="inlineStr"/>
       <c r="N29" s="1" t="inlineStr">
         <is>
-          <t>L80: isolated marker/symbol line :: 0</t>
+          <t>L77: isolated marker/symbol line :: S</t>
         </is>
       </c>
       <c r="O29" s="1" t="inlineStr">
         <is>
-          <t>L109: isolated marker/symbol line :: -</t>
+          <t>L99: symbol-only separator/garbage line :: 69—70</t>
         </is>
       </c>
       <c r="P29" s="1" t="inlineStr"/>
@@ -1885,12 +1845,12 @@
       <c r="M30" s="1" t="inlineStr"/>
       <c r="N30" s="1" t="inlineStr">
         <is>
-          <t>L82: symbol-only separator/garbage line :: 46-47</t>
+          <t>L79: isolated marker/symbol line :: 24</t>
         </is>
       </c>
       <c r="O30" s="1" t="inlineStr">
         <is>
-          <t>L137: isolated marker/symbol line :: 116</t>
+          <t>L101: symbol-only separator/garbage line :: . 108</t>
         </is>
       </c>
       <c r="P30" s="1" t="inlineStr"/>
@@ -1920,12 +1880,12 @@
       <c r="M31" s="1" t="inlineStr"/>
       <c r="N31" s="1" t="inlineStr">
         <is>
-          <t>L83: isolated marker/symbol line :: T</t>
+          <t>L80: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O31" s="1" t="inlineStr">
         <is>
-          <t>L139: isolated marker/symbol line :: .2</t>
+          <t>L103: isolated marker/symbol line :: 109</t>
         </is>
       </c>
       <c r="P31" s="1" t="inlineStr"/>
@@ -1955,12 +1915,12 @@
       <c r="M32" s="1" t="inlineStr"/>
       <c r="N32" s="1" t="inlineStr">
         <is>
-          <t>L86: isolated marker/symbol line :: 0</t>
+          <t>L82: symbol-only separator/garbage line :: 46-47</t>
         </is>
       </c>
       <c r="O32" s="1" t="inlineStr">
         <is>
-          <t>L147: isolated marker/symbol line :: 7</t>
+          <t>L105: symbol-only separator/garbage line :: . 111—112</t>
         </is>
       </c>
       <c r="P32" s="1" t="inlineStr"/>
@@ -1990,12 +1950,12 @@
       <c r="M33" s="1" t="inlineStr"/>
       <c r="N33" s="1" t="inlineStr">
         <is>
-          <t>L88: isolated marker/symbol line :: 113</t>
+          <t>L83: isolated marker/symbol line :: T</t>
         </is>
       </c>
       <c r="O33" s="1" t="inlineStr">
         <is>
-          <t>L149: symbol-only separator/garbage line :: .10</t>
+          <t>L107: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P33" s="1" t="inlineStr"/>
@@ -2025,12 +1985,12 @@
       <c r="M34" s="1" t="inlineStr"/>
       <c r="N34" s="1" t="inlineStr">
         <is>
-          <t>L91: symbol-only separator/garbage line :: 115-116</t>
+          <t>L86: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O34" s="1" t="inlineStr">
         <is>
-          <t>L153: symbol-only separator/garbage line :: .12</t>
+          <t>L109: isolated marker/symbol line :: -</t>
         </is>
       </c>
       <c r="P34" s="1" t="inlineStr"/>
@@ -2060,12 +2020,12 @@
       <c r="M35" s="1" t="inlineStr"/>
       <c r="N35" s="1" t="inlineStr">
         <is>
-          <t>L92: isolated marker/symbol line :: M</t>
+          <t>L88: isolated marker/symbol line :: 113</t>
         </is>
       </c>
       <c r="O35" s="1" t="inlineStr">
         <is>
-          <t>L155: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L137: isolated marker/symbol line :: 116</t>
         </is>
       </c>
       <c r="P35" s="1" t="inlineStr"/>
@@ -2095,12 +2055,12 @@
       <c r="M36" s="1" t="inlineStr"/>
       <c r="N36" s="1" t="inlineStr">
         <is>
-          <t>L94: isolated marker/symbol line :: S</t>
+          <t>L91: symbol-only separator/garbage line :: 115-116</t>
         </is>
       </c>
       <c r="O36" s="1" t="inlineStr">
         <is>
-          <t>L157: isolated marker/symbol line :: ]</t>
+          <t>L139: isolated marker/symbol line :: .2</t>
         </is>
       </c>
       <c r="P36" s="1" t="inlineStr"/>
@@ -2130,12 +2090,12 @@
       <c r="M37" s="1" t="inlineStr"/>
       <c r="N37" s="1" t="inlineStr">
         <is>
-          <t>L102: symbol-only separator/garbage line :: 69-70</t>
+          <t>L92: isolated marker/symbol line :: M</t>
         </is>
       </c>
       <c r="O37" s="1" t="inlineStr">
         <is>
-          <t>L159: isolated marker/symbol line :: 10</t>
+          <t>L145: symbol-only separator/garbage line :: . 7—10</t>
         </is>
       </c>
       <c r="P37" s="1" t="inlineStr"/>
@@ -2165,12 +2125,12 @@
       <c r="M38" s="1" t="inlineStr"/>
       <c r="N38" s="1" t="inlineStr">
         <is>
-          <t>L106: isolated marker/symbol line :: S</t>
+          <t>L94: isolated marker/symbol line :: S</t>
         </is>
       </c>
       <c r="O38" s="1" t="inlineStr">
         <is>
-          <t>L160: isolated marker/symbol line :: .7</t>
+          <t>L147: isolated marker/symbol line :: 7</t>
         </is>
       </c>
       <c r="P38" s="1" t="inlineStr"/>
@@ -2200,10 +2160,14 @@
       <c r="M39" s="1" t="inlineStr"/>
       <c r="N39" s="1" t="inlineStr">
         <is>
-          <t>L108: isolated marker/symbol line :: 108</t>
-        </is>
-      </c>
-      <c r="O39" s="1" t="inlineStr"/>
+          <t>L102: symbol-only separator/garbage line :: 69-70</t>
+        </is>
+      </c>
+      <c r="O39" s="1" t="inlineStr">
+        <is>
+          <t>L149: symbol-only separator/garbage line :: .10</t>
+        </is>
+      </c>
       <c r="P39" s="1" t="inlineStr"/>
       <c r="Q39" s="1" t="inlineStr"/>
       <c r="R39" s="1" t="inlineStr"/>
@@ -2231,10 +2195,14 @@
       <c r="M40" s="1" t="inlineStr"/>
       <c r="N40" s="1" t="inlineStr">
         <is>
-          <t>L111: isolated marker/symbol line :: 109</t>
-        </is>
-      </c>
-      <c r="O40" s="1" t="inlineStr"/>
+          <t>L104: stray/suspicious non-ASCII glyph(s): U+221A SQUARE ROOT | isolated marker/symbol line :: √</t>
+        </is>
+      </c>
+      <c r="O40" s="1" t="inlineStr">
+        <is>
+          <t>L153: symbol-only separator/garbage line :: .12</t>
+        </is>
+      </c>
       <c r="P40" s="1" t="inlineStr"/>
       <c r="Q40" s="1" t="inlineStr"/>
       <c r="R40" s="1" t="inlineStr"/>
@@ -2262,10 +2230,14 @@
       <c r="M41" s="1" t="inlineStr"/>
       <c r="N41" s="1" t="inlineStr">
         <is>
-          <t>L112: isolated marker/symbol line :: A</t>
-        </is>
-      </c>
-      <c r="O41" s="1" t="inlineStr"/>
+          <t>L106: isolated marker/symbol line :: S</t>
+        </is>
+      </c>
+      <c r="O41" s="1" t="inlineStr">
+        <is>
+          <t>L155: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
+        </is>
+      </c>
       <c r="P41" s="1" t="inlineStr"/>
       <c r="Q41" s="1" t="inlineStr"/>
       <c r="R41" s="1" t="inlineStr"/>
@@ -2293,10 +2265,14 @@
       <c r="M42" s="1" t="inlineStr"/>
       <c r="N42" s="1" t="inlineStr">
         <is>
-          <t>L117: isolated marker/symbol line :: 116</t>
-        </is>
-      </c>
-      <c r="O42" s="1" t="inlineStr"/>
+          <t>L108: isolated marker/symbol line :: 108</t>
+        </is>
+      </c>
+      <c r="O42" s="1" t="inlineStr">
+        <is>
+          <t>L157: isolated marker/symbol line :: ]</t>
+        </is>
+      </c>
       <c r="P42" s="1" t="inlineStr"/>
       <c r="Q42" s="1" t="inlineStr"/>
       <c r="R42" s="1" t="inlineStr"/>
@@ -2324,10 +2300,14 @@
       <c r="M43" s="1" t="inlineStr"/>
       <c r="N43" s="1" t="inlineStr">
         <is>
-          <t>L118: isolated marker/symbol line :: 2</t>
-        </is>
-      </c>
-      <c r="O43" s="1" t="inlineStr"/>
+          <t>L111: isolated marker/symbol line :: 109</t>
+        </is>
+      </c>
+      <c r="O43" s="1" t="inlineStr">
+        <is>
+          <t>L159: isolated marker/symbol line :: 10</t>
+        </is>
+      </c>
       <c r="P43" s="1" t="inlineStr"/>
       <c r="Q43" s="1" t="inlineStr"/>
       <c r="R43" s="1" t="inlineStr"/>
@@ -2355,10 +2335,14 @@
       <c r="M44" s="1" t="inlineStr"/>
       <c r="N44" s="1" t="inlineStr">
         <is>
-          <t>L120: isolated marker/symbol line :: 02</t>
-        </is>
-      </c>
-      <c r="O44" s="1" t="inlineStr"/>
+          <t>L112: isolated marker/symbol line :: A</t>
+        </is>
+      </c>
+      <c r="O44" s="1" t="inlineStr">
+        <is>
+          <t>L160: isolated marker/symbol line :: .7</t>
+        </is>
+      </c>
       <c r="P44" s="1" t="inlineStr"/>
       <c r="Q44" s="1" t="inlineStr"/>
       <c r="R44" s="1" t="inlineStr"/>
@@ -2386,7 +2370,7 @@
       <c r="M45" s="1" t="inlineStr"/>
       <c r="N45" s="1" t="inlineStr">
         <is>
-          <t>L122: stray/suspicious non-ASCII glyph(s): U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: â—�</t>
+          <t>L114: symbol-only separator/garbage line :: 111 — 112</t>
         </is>
       </c>
       <c r="O45" s="1" t="inlineStr"/>
@@ -2417,7 +2401,7 @@
       <c r="M46" s="1" t="inlineStr"/>
       <c r="N46" s="1" t="inlineStr">
         <is>
-          <t>L123: isolated marker/symbol line :: 2</t>
+          <t>L117: isolated marker/symbol line :: 116</t>
         </is>
       </c>
       <c r="O46" s="1" t="inlineStr"/>
@@ -2448,7 +2432,7 @@
       <c r="M47" s="1" t="inlineStr"/>
       <c r="N47" s="1" t="inlineStr">
         <is>
-          <t>L124: isolated marker/symbol line :: H</t>
+          <t>L118: isolated marker/symbol line :: 2</t>
         </is>
       </c>
       <c r="O47" s="1" t="inlineStr"/>
@@ -2479,7 +2463,7 @@
       <c r="M48" s="1" t="inlineStr"/>
       <c r="N48" s="1" t="inlineStr">
         <is>
-          <t>L126: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
+          <t>L120: isolated marker/symbol line :: 02</t>
         </is>
       </c>
       <c r="O48" s="1" t="inlineStr"/>
@@ -2510,7 +2494,7 @@
       <c r="M49" s="1" t="inlineStr"/>
       <c r="N49" s="1" t="inlineStr">
         <is>
-          <t>L130: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA, U+20AC EURO SIGN | isolated marker/symbol line :: ä¸€</t>
+          <t>L122: stray/suspicious non-ASCII glyph(s): U+25CF BLACK CIRCLE | isolated marker/symbol line :: ●</t>
         </is>
       </c>
       <c r="O49" s="1" t="inlineStr"/>
@@ -2541,7 +2525,7 @@
       <c r="M50" s="1" t="inlineStr"/>
       <c r="N50" s="1" t="inlineStr">
         <is>
-          <t>L132: symbol-only separator/garbage line :: . 7-10</t>
+          <t>L123: isolated marker/symbol line :: 2</t>
         </is>
       </c>
       <c r="O50" s="1" t="inlineStr"/>
@@ -2572,7 +2556,7 @@
       <c r="M51" s="1" t="inlineStr"/>
       <c r="N51" s="1" t="inlineStr">
         <is>
-          <t>L135: isolated marker/symbol line :: 7</t>
+          <t>L124: isolated marker/symbol line :: H</t>
         </is>
       </c>
       <c r="O51" s="1" t="inlineStr"/>
@@ -2603,7 +2587,7 @@
       <c r="M52" s="1" t="inlineStr"/>
       <c r="N52" s="1" t="inlineStr">
         <is>
-          <t>L136: isolated marker/symbol line :: H</t>
+          <t>L126: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
         </is>
       </c>
       <c r="O52" s="1" t="inlineStr"/>
@@ -2634,7 +2618,7 @@
       <c r="M53" s="1" t="inlineStr"/>
       <c r="N53" s="1" t="inlineStr">
         <is>
-          <t>L138: isolated marker/symbol line :: B</t>
+          <t>L130: stray/suspicious non-ASCII glyph(s): U+4E00 CJK UNIFIED IDEOGRAPH-4E00 | isolated marker/symbol line :: 一</t>
         </is>
       </c>
       <c r="O53" s="1" t="inlineStr"/>
@@ -2665,7 +2649,7 @@
       <c r="M54" s="1" t="inlineStr"/>
       <c r="N54" s="1" t="inlineStr">
         <is>
-          <t>L139: isolated marker/symbol line :: 10</t>
+          <t>L132: symbol-only separator/garbage line :: . 7-10</t>
         </is>
       </c>
       <c r="O54" s="1" t="inlineStr"/>
@@ -2696,7 +2680,7 @@
       <c r="M55" s="1" t="inlineStr"/>
       <c r="N55" s="1" t="inlineStr">
         <is>
-          <t>L144: isolated marker/symbol line :: 12</t>
+          <t>L135: isolated marker/symbol line :: 7</t>
         </is>
       </c>
       <c r="O55" s="1" t="inlineStr"/>
@@ -2727,7 +2711,7 @@
       <c r="M56" s="1" t="inlineStr"/>
       <c r="N56" s="1" t="inlineStr">
         <is>
-          <t>L148: isolated marker/symbol line :: 10</t>
+          <t>L136: isolated marker/symbol line :: H</t>
         </is>
       </c>
       <c r="O56" s="1" t="inlineStr"/>
@@ -2758,7 +2742,7 @@
       <c r="M57" s="1" t="inlineStr"/>
       <c r="N57" s="1" t="inlineStr">
         <is>
-          <t>L150: isolated marker/symbol line :: 7</t>
+          <t>L138: isolated marker/symbol line :: B</t>
         </is>
       </c>
       <c r="O57" s="1" t="inlineStr"/>
@@ -2773,6 +2757,161 @@
       <c r="X57" s="1" t="inlineStr"/>
       <c r="Y57" s="1" t="inlineStr"/>
     </row>
+    <row r="58">
+      <c r="A58" s="1" t="inlineStr"/>
+      <c r="B58" s="1" t="inlineStr"/>
+      <c r="C58" s="1" t="inlineStr"/>
+      <c r="D58" s="1" t="inlineStr"/>
+      <c r="E58" s="1" t="inlineStr"/>
+      <c r="F58" s="1" t="inlineStr"/>
+      <c r="G58" s="1" t="inlineStr"/>
+      <c r="H58" s="1" t="inlineStr"/>
+      <c r="I58" s="1" t="inlineStr"/>
+      <c r="J58" s="1" t="inlineStr"/>
+      <c r="K58" s="1" t="inlineStr"/>
+      <c r="L58" s="1" t="inlineStr"/>
+      <c r="M58" s="1" t="inlineStr"/>
+      <c r="N58" s="1" t="inlineStr">
+        <is>
+          <t>L139: isolated marker/symbol line :: 10</t>
+        </is>
+      </c>
+      <c r="O58" s="1" t="inlineStr"/>
+      <c r="P58" s="1" t="inlineStr"/>
+      <c r="Q58" s="1" t="inlineStr"/>
+      <c r="R58" s="1" t="inlineStr"/>
+      <c r="S58" s="1" t="inlineStr"/>
+      <c r="T58" s="1" t="inlineStr"/>
+      <c r="U58" s="1" t="inlineStr"/>
+      <c r="V58" s="1" t="inlineStr"/>
+      <c r="W58" s="1" t="inlineStr"/>
+      <c r="X58" s="1" t="inlineStr"/>
+      <c r="Y58" s="1" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="1" t="inlineStr"/>
+      <c r="B59" s="1" t="inlineStr"/>
+      <c r="C59" s="1" t="inlineStr"/>
+      <c r="D59" s="1" t="inlineStr"/>
+      <c r="E59" s="1" t="inlineStr"/>
+      <c r="F59" s="1" t="inlineStr"/>
+      <c r="G59" s="1" t="inlineStr"/>
+      <c r="H59" s="1" t="inlineStr"/>
+      <c r="I59" s="1" t="inlineStr"/>
+      <c r="J59" s="1" t="inlineStr"/>
+      <c r="K59" s="1" t="inlineStr"/>
+      <c r="L59" s="1" t="inlineStr"/>
+      <c r="M59" s="1" t="inlineStr"/>
+      <c r="N59" s="1" t="inlineStr">
+        <is>
+          <t>L144: isolated marker/symbol line :: 12</t>
+        </is>
+      </c>
+      <c r="O59" s="1" t="inlineStr"/>
+      <c r="P59" s="1" t="inlineStr"/>
+      <c r="Q59" s="1" t="inlineStr"/>
+      <c r="R59" s="1" t="inlineStr"/>
+      <c r="S59" s="1" t="inlineStr"/>
+      <c r="T59" s="1" t="inlineStr"/>
+      <c r="U59" s="1" t="inlineStr"/>
+      <c r="V59" s="1" t="inlineStr"/>
+      <c r="W59" s="1" t="inlineStr"/>
+      <c r="X59" s="1" t="inlineStr"/>
+      <c r="Y59" s="1" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="1" t="inlineStr"/>
+      <c r="B60" s="1" t="inlineStr"/>
+      <c r="C60" s="1" t="inlineStr"/>
+      <c r="D60" s="1" t="inlineStr"/>
+      <c r="E60" s="1" t="inlineStr"/>
+      <c r="F60" s="1" t="inlineStr"/>
+      <c r="G60" s="1" t="inlineStr"/>
+      <c r="H60" s="1" t="inlineStr"/>
+      <c r="I60" s="1" t="inlineStr"/>
+      <c r="J60" s="1" t="inlineStr"/>
+      <c r="K60" s="1" t="inlineStr"/>
+      <c r="L60" s="1" t="inlineStr"/>
+      <c r="M60" s="1" t="inlineStr"/>
+      <c r="N60" s="1" t="inlineStr">
+        <is>
+          <t>L146: stray/suspicious non-ASCII glyph(s): U+5206 CJK UNIFIED IDEOGRAPH-5206 | isolated marker/symbol line :: 分</t>
+        </is>
+      </c>
+      <c r="O60" s="1" t="inlineStr"/>
+      <c r="P60" s="1" t="inlineStr"/>
+      <c r="Q60" s="1" t="inlineStr"/>
+      <c r="R60" s="1" t="inlineStr"/>
+      <c r="S60" s="1" t="inlineStr"/>
+      <c r="T60" s="1" t="inlineStr"/>
+      <c r="U60" s="1" t="inlineStr"/>
+      <c r="V60" s="1" t="inlineStr"/>
+      <c r="W60" s="1" t="inlineStr"/>
+      <c r="X60" s="1" t="inlineStr"/>
+      <c r="Y60" s="1" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="1" t="inlineStr"/>
+      <c r="B61" s="1" t="inlineStr"/>
+      <c r="C61" s="1" t="inlineStr"/>
+      <c r="D61" s="1" t="inlineStr"/>
+      <c r="E61" s="1" t="inlineStr"/>
+      <c r="F61" s="1" t="inlineStr"/>
+      <c r="G61" s="1" t="inlineStr"/>
+      <c r="H61" s="1" t="inlineStr"/>
+      <c r="I61" s="1" t="inlineStr"/>
+      <c r="J61" s="1" t="inlineStr"/>
+      <c r="K61" s="1" t="inlineStr"/>
+      <c r="L61" s="1" t="inlineStr"/>
+      <c r="M61" s="1" t="inlineStr"/>
+      <c r="N61" s="1" t="inlineStr">
+        <is>
+          <t>L148: isolated marker/symbol line :: 10</t>
+        </is>
+      </c>
+      <c r="O61" s="1" t="inlineStr"/>
+      <c r="P61" s="1" t="inlineStr"/>
+      <c r="Q61" s="1" t="inlineStr"/>
+      <c r="R61" s="1" t="inlineStr"/>
+      <c r="S61" s="1" t="inlineStr"/>
+      <c r="T61" s="1" t="inlineStr"/>
+      <c r="U61" s="1" t="inlineStr"/>
+      <c r="V61" s="1" t="inlineStr"/>
+      <c r="W61" s="1" t="inlineStr"/>
+      <c r="X61" s="1" t="inlineStr"/>
+      <c r="Y61" s="1" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="1" t="inlineStr"/>
+      <c r="B62" s="1" t="inlineStr"/>
+      <c r="C62" s="1" t="inlineStr"/>
+      <c r="D62" s="1" t="inlineStr"/>
+      <c r="E62" s="1" t="inlineStr"/>
+      <c r="F62" s="1" t="inlineStr"/>
+      <c r="G62" s="1" t="inlineStr"/>
+      <c r="H62" s="1" t="inlineStr"/>
+      <c r="I62" s="1" t="inlineStr"/>
+      <c r="J62" s="1" t="inlineStr"/>
+      <c r="K62" s="1" t="inlineStr"/>
+      <c r="L62" s="1" t="inlineStr"/>
+      <c r="M62" s="1" t="inlineStr"/>
+      <c r="N62" s="1" t="inlineStr">
+        <is>
+          <t>L150: isolated marker/symbol line :: 7</t>
+        </is>
+      </c>
+      <c r="O62" s="1" t="inlineStr"/>
+      <c r="P62" s="1" t="inlineStr"/>
+      <c r="Q62" s="1" t="inlineStr"/>
+      <c r="R62" s="1" t="inlineStr"/>
+      <c r="S62" s="1" t="inlineStr"/>
+      <c r="T62" s="1" t="inlineStr"/>
+      <c r="U62" s="1" t="inlineStr"/>
+      <c r="V62" s="1" t="inlineStr"/>
+      <c r="W62" s="1" t="inlineStr"/>
+      <c r="X62" s="1" t="inlineStr"/>
+      <c r="Y62" s="1" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
